--- a/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>579.4122180816186</v>
+        <v>580.5528593122239</v>
       </c>
       <c r="E2" t="n">
-        <v>19256.57473152989</v>
+        <v>19618.56144424486</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6424428244570088</v>
+        <v>0.6497929324857714</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4944072440676888</v>
+        <v>0.4944292353336619</v>
       </c>
       <c r="H2" t="n">
-        <v>1.299420330437255</v>
+        <v>1.314228379006074</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>227.0186620039526</v>
+        <v>226.333672893159</v>
       </c>
       <c r="E3" t="n">
-        <v>7878.808371328552</v>
+        <v>7327.223235908057</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2596310624020235</v>
+        <v>0.2576749423417579</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5926004424333164</v>
+        <v>0.5926077120271671</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4381216141789145</v>
+        <v>0.4348153713023992</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8905669917382492</v>
+        <v>0.8904611265821758</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067440656772295</v>
+        <v>1.067279386335006</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>38.22949669084406</v>
+        <v>37.98428605942213</v>
       </c>
       <c r="E4" t="n">
-        <v>894.3299343340367</v>
+        <v>888.853365348234</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3031676301801627</v>
+        <v>-0.3072653182286074</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5573150218553491</v>
+        <v>0.5573154855337638</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5439789316478352</v>
+        <v>-0.5513310256116908</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7364981385238182</v>
+        <v>0.7364121824143852</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8302092679524529</v>
+        <v>0.8300761436938227</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>37.18633889413569</v>
+        <v>36.95074561617071</v>
       </c>
       <c r="E5" t="n">
-        <v>1431.235663861672</v>
+        <v>1296.600021556121</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7401791844358201</v>
+        <v>0.7313328322654054</v>
       </c>
       <c r="G5" t="n">
-        <v>1.09868268265444</v>
+        <v>1.098719999051188</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6736969610256636</v>
+        <v>0.6656225725361842</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4737435458381883</v>
+        <v>0.4736170045876378</v>
       </c>
       <c r="N5" t="n">
-        <v>1.052763356680241</v>
+        <v>1.052471087151604</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.95074683247421</v>
+        <v>10.9314919256836</v>
       </c>
       <c r="E6" t="n">
-        <v>370.962816041115</v>
+        <v>334.9590373537013</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.477232849853398</v>
+        <v>-0.4763410476949862</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8086868448645479</v>
+        <v>0.8086812012334926</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5901330692888083</v>
+        <v>-0.5890344018983211</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6664079671810761</v>
+        <v>0.6663631436119914</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090023179956642</v>
+        <v>1.089893778368942</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.89002077531948</v>
+        <v>10.82079394597803</v>
       </c>
       <c r="E7" t="n">
-        <v>257.297675881147</v>
+        <v>230.3524695177869</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.2998335601404936</v>
+        <v>-0.3028297566534816</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7088072182410781</v>
+        <v>0.7088208399634717</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4230114372770323</v>
+        <v>-0.4272303233481222</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7502314427651033</v>
+        <v>0.7501251811530885</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075569721851647</v>
+        <v>1.075390213573974</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.744342778720238</v>
+        <v>9.686296792911342</v>
       </c>
       <c r="E8" t="n">
-        <v>437.8479765871599</v>
+        <v>409.6776030813898</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3321911795935837</v>
+        <v>-0.3344043401168769</v>
       </c>
       <c r="G8" t="n">
-        <v>1.162096076249403</v>
+        <v>1.162105454800613</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.285855177022636</v>
+        <v>-0.2877573104363855</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7371567110531334</v>
+        <v>0.7370783154620537</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732674696365246</v>
+        <v>1.732427352188538</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.039411936366471</v>
+        <v>7.032548834281001</v>
       </c>
       <c r="E9" t="n">
-        <v>219.5904082407594</v>
+        <v>213.4465678989998</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3326943124285526</v>
+        <v>0.3329195621002567</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4804986769252262</v>
+        <v>0.4804977392664733</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6923938158529529</v>
+        <v>0.692863951053112</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6734182344418361</v>
+        <v>0.6733409257240032</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6544737654012279</v>
+        <v>0.6543682481632385</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.889072508495588</v>
+        <v>6.823486686821941</v>
       </c>
       <c r="E10" t="n">
-        <v>795.1028498305599</v>
+        <v>767.7203437169018</v>
       </c>
       <c r="F10" t="n">
-        <v>1.020771091168263</v>
+        <v>1.006434671755402</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8151784199049065</v>
+        <v>0.8152692226855315</v>
       </c>
       <c r="H10" t="n">
-        <v>1.252205733423782</v>
+        <v>1.234481375906922</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.66380337087884</v>
+        <v>0.6635408635806815</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094478670151684</v>
+        <v>1.094119047605351</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.535251254570846</v>
+        <v>6.497262891906773</v>
       </c>
       <c r="E11" t="n">
-        <v>306.8568360981989</v>
+        <v>289.6773091143865</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2863706736436137</v>
+        <v>-0.2894811644109514</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9508189185283802</v>
+        <v>0.9508411284496593</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3011831885789997</v>
+        <v>-0.3044474578870486</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7133563160122934</v>
+        <v>0.7132391759820698</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371890661099085</v>
+        <v>1.371636413222275</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.415247543662555</v>
+        <v>6.288711828017743</v>
       </c>
       <c r="E12" t="n">
-        <v>128.0065671560988</v>
+        <v>120.2990412325442</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2749203572264344</v>
+        <v>-0.2752907643911077</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6531257800673049</v>
+        <v>0.6531274843975667</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4209301877474561</v>
+        <v>-0.4214962177637204</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7889625917613651</v>
+        <v>0.7888912915149305</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042241622409392</v>
+        <v>1.042103799429627</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.779187319886893</v>
+        <v>4.756972394992224</v>
       </c>
       <c r="E13" t="n">
-        <v>252.558871625714</v>
+        <v>248.1871639882948</v>
       </c>
       <c r="F13" t="n">
-        <v>1.740602736663166</v>
+        <v>1.721381060243526</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8552394368010676</v>
+        <v>0.855267873447967</v>
       </c>
       <c r="H13" t="n">
-        <v>2.035222724496553</v>
+        <v>2.012680604152556</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6005950318635319</v>
+        <v>0.6004713494799994</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038926033062255</v>
+        <v>1.038700419463698</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.46542358740972</v>
+        <v>4.44901295056469</v>
       </c>
       <c r="E14" t="n">
-        <v>122.9720634073594</v>
+        <v>110.5457743052856</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4151751311475405</v>
+        <v>-0.4163810746493425</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8429615758467446</v>
+        <v>0.842965999742025</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4925196391431034</v>
+        <v>-0.4939476500555997</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7598905817194324</v>
+        <v>0.7598213330594755</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295609176287907</v>
+        <v>1.295440285232244</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.21757937303331</v>
+        <v>4.140436565882561</v>
       </c>
       <c r="E15" t="n">
-        <v>160.2958992210625</v>
+        <v>152.9571112406984</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5414430930453886</v>
+        <v>0.5083615800936307</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9537829645834376</v>
+        <v>0.9539420133947457</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5676795593448899</v>
+        <v>0.532906165108034</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5139659298438959</v>
+        <v>0.5136795806994942</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9915144936555171</v>
+        <v>0.9910832500055493</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.104537028489641</v>
+        <v>4.128461489201413</v>
       </c>
       <c r="E16" t="n">
-        <v>232.7750327288593</v>
+        <v>218.3105600814021</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.04117485024608092</v>
+        <v>-0.02878342240149567</v>
       </c>
       <c r="G16" t="n">
-        <v>0.788367552279613</v>
+        <v>0.7883721897520636</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.05222798696752717</v>
+        <v>-0.0365099413394425</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7130930747803969</v>
+        <v>0.7131404031775963</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137077679701629</v>
+        <v>1.137109258667484</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.843258071807325</v>
+        <v>3.83723183525623</v>
       </c>
       <c r="E17" t="n">
-        <v>148.0427389380866</v>
+        <v>135.7479090254953</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.06093564332691304</v>
+        <v>-0.06018450298649736</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7500706165606581</v>
+        <v>0.7500627638258703</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.08123987526177834</v>
+        <v>-0.080239289148967</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7209834040193429</v>
+        <v>0.7208743956950617</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093811777379119</v>
+        <v>1.093586307131402</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.112548972317841</v>
+        <v>3.116784217837576</v>
       </c>
       <c r="E18" t="n">
-        <v>80.88689333958564</v>
+        <v>77.2585500068501</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4619115211376413</v>
+        <v>-0.4603197858055678</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7395380605113877</v>
+        <v>0.7395448471454095</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6245946568567834</v>
+        <v>-0.622436607573387</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645341666960516</v>
+        <v>0.7645335699526903</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143595935571849</v>
+        <v>1.143554672180005</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.941923294606426</v>
+        <v>2.935096743817935</v>
       </c>
       <c r="E19" t="n">
-        <v>118.2377470028201</v>
+        <v>117.6069023778238</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09874904858336175</v>
+        <v>0.09511830151145295</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4773793331980624</v>
+        <v>0.4773789842588035</v>
       </c>
       <c r="H19" t="n">
-        <v>0.2068565639861734</v>
+        <v>0.1992511288680569</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.716325376290654</v>
+        <v>0.7162609669709877</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6916543691250333</v>
+        <v>0.6915609119393822</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.637732062724611</v>
+        <v>2.625342458804174</v>
       </c>
       <c r="E20" t="n">
-        <v>134.810494442353</v>
+        <v>127.3167720346946</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3002767025234415</v>
+        <v>-0.3032823081498598</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7717585864670831</v>
+        <v>0.7717665565043555</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3890811294993591</v>
+        <v>-0.3929715606278</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.731726856077326</v>
+        <v>0.7316426247155531</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142209162390277</v>
+        <v>1.142038675539637</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>580.5528593122239</v>
+        <v>576.3456984987951</v>
       </c>
       <c r="E2" t="n">
-        <v>19618.56144424486</v>
+        <v>19640.65804843159</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6497929324857714</v>
+        <v>0.6353296986936028</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4944292353336619</v>
+        <v>0.4944147548500161</v>
       </c>
       <c r="H2" t="n">
-        <v>1.314228379006074</v>
+        <v>1.285013629672792</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>226.333672893159</v>
+        <v>225.6854414754007</v>
       </c>
       <c r="E3" t="n">
-        <v>7327.223235908057</v>
+        <v>7021.826183984107</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2576749423417579</v>
+        <v>0.2531938812686165</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5926077120271671</v>
+        <v>0.5926357647462908</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4348153713023992</v>
+        <v>0.4272335493910153</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8904611265821758</v>
+        <v>0.8905760400035697</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067279386335006</v>
+        <v>1.067498911298361</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.98428605942213</v>
+        <v>37.79684675016127</v>
       </c>
       <c r="E4" t="n">
-        <v>888.853365348234</v>
+        <v>879.9736192264156</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3072653182286074</v>
+        <v>-0.3113570382719065</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5573154855337638</v>
+        <v>0.5573622708216396</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5513310256116908</v>
+        <v>-0.5586259683722713</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7364121824143852</v>
+        <v>0.7364962993025029</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8300761436938227</v>
+        <v>0.8302649664157036</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.95074561617071</v>
+        <v>36.92737267732074</v>
       </c>
       <c r="E5" t="n">
-        <v>1296.600021556121</v>
+        <v>1252.065135020536</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7313328322654054</v>
+        <v>0.729368486891973</v>
       </c>
       <c r="G5" t="n">
-        <v>1.098719999051188</v>
+        <v>1.098730651880483</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6656225725361842</v>
+        <v>0.6638282873456339</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4736170045876378</v>
+        <v>0.4737934340090236</v>
       </c>
       <c r="N5" t="n">
-        <v>1.052471087151604</v>
+        <v>1.052904193288782</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.9314919256836</v>
+        <v>10.87741639020466</v>
       </c>
       <c r="E6" t="n">
-        <v>334.9590373537013</v>
+        <v>310.860127169613</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4763410476949862</v>
+        <v>-0.4798169544977818</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8086812012334926</v>
+        <v>0.8087181994333101</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5890344018983211</v>
+        <v>-0.5933054985457259</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6663631436119914</v>
+        <v>0.6664384670666658</v>
       </c>
       <c r="N6" t="n">
-        <v>1.089893778368942</v>
+        <v>1.090098771997099</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.82079394597803</v>
+        <v>10.76039863753911</v>
       </c>
       <c r="E7" t="n">
-        <v>230.3524695177869</v>
+        <v>220.9582621718056</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3028297566534816</v>
+        <v>-0.307916007964567</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7088208399634717</v>
+        <v>0.7088880137323355</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4272303233481222</v>
+        <v>-0.4343648108018808</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7501251811530885</v>
+        <v>0.7502241698369181</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075390213573974</v>
+        <v>1.075665554866007</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.686296792911342</v>
+        <v>9.582478547952038</v>
       </c>
       <c r="E8" t="n">
-        <v>409.6776030813898</v>
+        <v>400.5732672583845</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3344043401168769</v>
+        <v>-0.344341081681801</v>
       </c>
       <c r="G8" t="n">
-        <v>1.162105454800613</v>
+        <v>1.162234415404492</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2877573104363855</v>
+        <v>-0.2962750690547743</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7370783154620537</v>
+        <v>0.7371515984357879</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732427352188538</v>
+        <v>1.732842615775905</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>7.032548834281001</v>
+        <v>6.982636471997067</v>
       </c>
       <c r="E9" t="n">
-        <v>213.4465678989998</v>
+        <v>211.0287569059848</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3329195621002567</v>
+        <v>0.3182978937578507</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4804977392664733</v>
+        <v>0.4806502499572395</v>
       </c>
       <c r="H9" t="n">
-        <v>0.692863951053112</v>
+        <v>0.6622235061485304</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6733409257240032</v>
+        <v>0.6733577886581367</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6543682481632385</v>
+        <v>0.654611510385382</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.823486686821941</v>
+        <v>6.799914095265365</v>
       </c>
       <c r="E10" t="n">
-        <v>767.7203437169018</v>
+        <v>752.824827922977</v>
       </c>
       <c r="F10" t="n">
-        <v>1.006434671755402</v>
+        <v>0.9946976185274679</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8152692226855315</v>
+        <v>0.8153776136046071</v>
       </c>
       <c r="H10" t="n">
-        <v>1.234481375906922</v>
+        <v>1.219922649249746</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6635408635806815</v>
+        <v>0.6637944874968243</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094119047605351</v>
+        <v>1.094714831686694</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.497262891906773</v>
+        <v>6.467297508344518</v>
       </c>
       <c r="E11" t="n">
-        <v>289.6773091143865</v>
+        <v>284.1396761175929</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2894811644109514</v>
+        <v>-0.2938032226741866</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9508411284496593</v>
+        <v>0.9508966052323552</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3044474578870486</v>
+        <v>-0.3089749411844778</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7132391759820698</v>
+        <v>0.7133717486579386</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371636413222275</v>
+        <v>1.372011590295849</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.288711828017743</v>
+        <v>6.256286147839639</v>
       </c>
       <c r="E12" t="n">
-        <v>120.2990412325442</v>
+        <v>117.0068445724404</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2752907643911077</v>
+        <v>-0.2799169117774328</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6531274843975667</v>
+        <v>0.6531737272758482</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4214962177637204</v>
+        <v>-0.428548945079076</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7888912915149305</v>
+        <v>0.7889721249116061</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042103799429627</v>
+        <v>1.042314895520443</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.756972394992224</v>
+        <v>4.720131009402111</v>
       </c>
       <c r="E13" t="n">
-        <v>248.1871639882948</v>
+        <v>240.9494762905218</v>
       </c>
       <c r="F13" t="n">
-        <v>1.721381060243526</v>
+        <v>1.693347988149502</v>
       </c>
       <c r="G13" t="n">
-        <v>0.855267873447967</v>
+        <v>0.8553868816490128</v>
       </c>
       <c r="H13" t="n">
-        <v>2.012680604152556</v>
+        <v>1.979628194537038</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6004713494799994</v>
+        <v>0.6005921607744972</v>
       </c>
       <c r="N13" t="n">
-        <v>1.038700419463698</v>
+        <v>1.039084393230913</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.44901295056469</v>
+        <v>4.424893671169724</v>
       </c>
       <c r="E14" t="n">
-        <v>110.5457743052856</v>
+        <v>106.8632862878833</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4163810746493425</v>
+        <v>-0.4199952178581214</v>
       </c>
       <c r="G14" t="n">
-        <v>0.842965999742025</v>
+        <v>0.8430017024902569</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4939476500555997</v>
+        <v>-0.4982139616295444</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7598213330594755</v>
+        <v>0.7599025600405831</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295440285232244</v>
+        <v>1.29567159061676</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.140436565882561</v>
+        <v>4.133119658777107</v>
       </c>
       <c r="E15" t="n">
-        <v>152.9571112406984</v>
+        <v>149.4823896803672</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5083615800936307</v>
+        <v>0.5070420077779556</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9539420133947457</v>
+        <v>0.953955926393109</v>
       </c>
       <c r="H15" t="n">
-        <v>0.532906165108034</v>
+        <v>0.53151512952498</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5136795806994942</v>
+        <v>0.5139733068220214</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9910832500055493</v>
+        <v>0.9916934663478418</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.128461489201413</v>
+        <v>4.106830103561442</v>
       </c>
       <c r="E16" t="n">
-        <v>218.3105600814021</v>
+        <v>208.4757038461634</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.02878342240149567</v>
+        <v>-0.0373276643147884</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7883721897520636</v>
+        <v>0.7883523130277983</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.0365099413394425</v>
+        <v>-0.04734896276440833</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7131404031775963</v>
+        <v>0.7131207765246627</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137109258667484</v>
+        <v>1.137082597407396</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.83723183525623</v>
+        <v>3.814519065158756</v>
       </c>
       <c r="E17" t="n">
-        <v>135.7479090254953</v>
+        <v>128.3009250829611</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.06018450298649736</v>
+        <v>-0.07068696699298516</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7500627638258703</v>
+        <v>0.7502295302697783</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.080239289148967</v>
+        <v>-0.09422045406232746</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7208743956950617</v>
+        <v>0.7209787638688332</v>
       </c>
       <c r="N17" t="n">
-        <v>1.093586307131402</v>
+        <v>1.094019856903109</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.116784217837576</v>
+        <v>3.095230958378171</v>
       </c>
       <c r="E18" t="n">
-        <v>77.2585500068501</v>
+        <v>75.41245471669883</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4603197858055678</v>
+        <v>-0.465091509551372</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7395448471454095</v>
+        <v>0.7395508284099774</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.622436607573387</v>
+        <v>-0.6288837652326229</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645335699526903</v>
+        <v>0.7645421496246777</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143554672180005</v>
+        <v>1.143610247394009</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.935096743817935</v>
+        <v>2.929518120950719</v>
       </c>
       <c r="E19" t="n">
-        <v>117.6069023778238</v>
+        <v>115.0633703451547</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09511830151145295</v>
+        <v>0.09421107793841177</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4773789842588035</v>
+        <v>0.477381564977969</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1992511288680569</v>
+        <v>0.1973496357002382</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7162609669709877</v>
+        <v>0.7163308766639734</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6915609119393822</v>
+        <v>0.6916524063842409</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.625342458804174</v>
+        <v>2.607829955197645</v>
       </c>
       <c r="E20" t="n">
-        <v>127.3167720346946</v>
+        <v>125.4301115533643</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3032823081498598</v>
+        <v>-0.3097834881231069</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7717665565043555</v>
+        <v>0.7718448307118235</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.3929715606278</v>
+        <v>-0.4013546192146071</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7316426247155531</v>
+        <v>0.7317201405949403</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142038675539637</v>
+        <v>1.142308967331004</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>576.3456984987951</v>
+        <v>575.8765165020214</v>
       </c>
       <c r="E2" t="n">
-        <v>19640.65804843159</v>
+        <v>19712.32895053934</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6353296986936028</v>
+        <v>0.6329023570826868</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4944147548500161</v>
+        <v>0.494423815580008</v>
       </c>
       <c r="H2" t="n">
-        <v>1.285013629672792</v>
+        <v>1.28008064567082</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>225.6854414754007</v>
+        <v>223.5303876133367</v>
       </c>
       <c r="E3" t="n">
-        <v>7021.826183984107</v>
+        <v>6958.947030582772</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2531938812686165</v>
+        <v>0.2510529355988753</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5926357647462908</v>
+        <v>0.5926547794660878</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4272335493910153</v>
+        <v>0.4236073753172875</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8905760400035697</v>
+        <v>0.8905822221340887</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067498911298361</v>
+        <v>1.0675210089468</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.79684675016127</v>
+        <v>37.68403686312427</v>
       </c>
       <c r="E4" t="n">
-        <v>879.9736192264156</v>
+        <v>865.3123586211194</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3113570382719065</v>
+        <v>-0.314700357668753</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5573622708216396</v>
+        <v>0.55743499600059</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5586259683722713</v>
+        <v>-0.5645507726042015</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7364962993025029</v>
+        <v>0.7364848021760645</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8302649664157036</v>
+        <v>0.8303451205599856</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.92737267732074</v>
+        <v>36.74464262082466</v>
       </c>
       <c r="E5" t="n">
-        <v>1252.065135020536</v>
+        <v>1230.899816112102</v>
       </c>
       <c r="F5" t="n">
-        <v>0.729368486891973</v>
+        <v>0.7153067931177821</v>
       </c>
       <c r="G5" t="n">
-        <v>1.098730651880483</v>
+        <v>1.098832110801617</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6638282873456339</v>
+        <v>0.6509700490969027</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4737934340090236</v>
+        <v>0.4738235854311152</v>
       </c>
       <c r="N5" t="n">
-        <v>1.052904193288782</v>
+        <v>1.053049133395983</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.87741639020466</v>
+        <v>10.82802819255333</v>
       </c>
       <c r="E6" t="n">
-        <v>310.860127169613</v>
+        <v>310.4939426577779</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4798169544977818</v>
+        <v>-0.4834649475966609</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8087181994333101</v>
+        <v>0.8088005567740305</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5933054985457259</v>
+        <v>-0.5977554584346502</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6664384670666658</v>
+        <v>0.6664464641587571</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090098771997099</v>
+        <v>1.090202887252428</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.76039863753911</v>
+        <v>10.72052077786725</v>
       </c>
       <c r="E7" t="n">
-        <v>220.9582621718056</v>
+        <v>214.2874053646151</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.307916007964567</v>
+        <v>-0.310903624973178</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7088880137323355</v>
+        <v>0.7089534146337595</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4343648108018808</v>
+        <v>-0.4385388638459252</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7502241698369181</v>
+        <v>0.7502239380911327</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075665554866007</v>
+        <v>1.075744747501198</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.582478547952038</v>
+        <v>9.584627089968258</v>
       </c>
       <c r="E8" t="n">
-        <v>400.5732672583845</v>
+        <v>394.8822984816207</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.344341081681801</v>
+        <v>-0.3417684303996634</v>
       </c>
       <c r="G8" t="n">
-        <v>1.162234415404492</v>
+        <v>1.162187350566213</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2962750690547743</v>
+        <v>-0.2940734385322256</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7371515984357879</v>
+        <v>0.7371841901802245</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732842615775905</v>
+        <v>1.732817299384752</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.982636471997067</v>
+        <v>6.948698901289175</v>
       </c>
       <c r="E9" t="n">
-        <v>211.0287569059848</v>
+        <v>212.0888362041927</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3182978937578507</v>
+        <v>0.3117872321026123</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4806502499572395</v>
+        <v>0.4807782622182382</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6622235061485304</v>
+        <v>0.6485052603336788</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6733577886581367</v>
+        <v>0.67330680851382</v>
       </c>
       <c r="N9" t="n">
-        <v>0.654611510385382</v>
+        <v>0.6547242813480518</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.799914095265365</v>
+        <v>6.779343417309995</v>
       </c>
       <c r="E10" t="n">
-        <v>752.824827922977</v>
+        <v>749.1763737277113</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9946976185274679</v>
+        <v>0.9864060648148931</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8153776136046071</v>
+        <v>0.8154727358407379</v>
       </c>
       <c r="H10" t="n">
-        <v>1.219922649249746</v>
+        <v>1.209612561476903</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6637944874968243</v>
+        <v>0.6638052325525937</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094714831686694</v>
+        <v>1.094840199839574</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.467297508344518</v>
+        <v>6.456358794273865</v>
       </c>
       <c r="E11" t="n">
-        <v>284.1396761175929</v>
+        <v>280.540205857912</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2938032226741866</v>
+        <v>-0.2952874271001634</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9508966052323552</v>
+        <v>0.9509222794261714</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3089749411844778</v>
+        <v>-0.3105274042778269</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7133717486579386</v>
+        <v>0.713389814307351</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372011590295849</v>
+        <v>1.372058236201172</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.256286147839639</v>
+        <v>6.249154143490162</v>
       </c>
       <c r="E12" t="n">
-        <v>117.0068445724404</v>
+        <v>113.684273135819</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2799169117774328</v>
+        <v>-0.2813957347757193</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6531737272758482</v>
+        <v>0.6531982777944717</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.428548945079076</v>
+        <v>-0.4307968106190572</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7889721249116061</v>
+        <v>0.7889832050813537</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042314895520443</v>
+        <v>1.042349608833733</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.720131009402111</v>
+        <v>4.696413371457807</v>
       </c>
       <c r="E13" t="n">
-        <v>240.9494762905218</v>
+        <v>239.993345015895</v>
       </c>
       <c r="F13" t="n">
-        <v>1.693347988149502</v>
+        <v>1.675679840000468</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8553868816490128</v>
+        <v>0.8555094149172855</v>
       </c>
       <c r="H13" t="n">
-        <v>1.979628194537038</v>
+        <v>1.95869245946578</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6005921607744972</v>
+        <v>0.6005980990366041</v>
       </c>
       <c r="N13" t="n">
-        <v>1.039084393230913</v>
+        <v>1.039224471225118</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.424893671169724</v>
+        <v>4.421976541910248</v>
       </c>
       <c r="E14" t="n">
-        <v>106.8632862878833</v>
+        <v>104.1277652798429</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4199952178581214</v>
+        <v>-0.4205970364818402</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8430017024902569</v>
+        <v>0.8430109239452438</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4982139616295444</v>
+        <v>-0.4989224036545929</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7599025600405831</v>
+        <v>0.7599146512540426</v>
       </c>
       <c r="N14" t="n">
-        <v>1.29567159061676</v>
+        <v>1.295682635193638</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.133119658777107</v>
+        <v>4.101211921255932</v>
       </c>
       <c r="E15" t="n">
-        <v>149.4823896803672</v>
+        <v>147.5491930141609</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5070420077779556</v>
+        <v>0.4885979610156619</v>
       </c>
       <c r="G15" t="n">
-        <v>0.953955926393109</v>
+        <v>0.9542116661005449</v>
       </c>
       <c r="H15" t="n">
-        <v>0.53151512952498</v>
+        <v>0.5120435835922578</v>
       </c>
       <c r="I15" t="n">
         <v>0.3858131487889274</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5139733068220214</v>
+        <v>0.5139669849049293</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9916934663478418</v>
+        <v>0.9919289434136169</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.106830103561442</v>
+        <v>4.097146118200017</v>
       </c>
       <c r="E16" t="n">
-        <v>208.4757038461634</v>
+        <v>203.2867635221655</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.0373276643147884</v>
+        <v>-0.04084046317729484</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7883523130277983</v>
+        <v>0.7883656298825156</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.04734896276440833</v>
+        <v>-0.05180396205676926</v>
       </c>
       <c r="I16" t="n">
         <v>0.4268646717284502</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7131207765246627</v>
+        <v>0.7131348773705052</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137082597407396</v>
+        <v>1.137103450669867</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.814519065158756</v>
+        <v>3.796047122553254</v>
       </c>
       <c r="E17" t="n">
-        <v>128.3009250829611</v>
+        <v>117.8100073090976</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.07068696699298516</v>
+        <v>-0.07312087109618692</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7502295302697783</v>
+        <v>0.7502857442426906</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.09422045406232746</v>
+        <v>-0.0974573642872454</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7209787638688332</v>
+        <v>0.7209978936292685</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094019856903109</v>
+        <v>1.094110809740132</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.095230958378171</v>
+        <v>3.092756201356205</v>
       </c>
       <c r="E18" t="n">
-        <v>75.41245471669883</v>
+        <v>74.43706215837071</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.465091509551372</v>
+        <v>-0.4655681066927082</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7395508284099774</v>
+        <v>0.7395557727634073</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6288837652326229</v>
+        <v>-0.6295239978359941</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645421496246777</v>
+        <v>0.764547079168882</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143610247394009</v>
+        <v>1.143604308957991</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.929518120950719</v>
+        <v>2.919436212642301</v>
       </c>
       <c r="E19" t="n">
-        <v>115.0633703451547</v>
+        <v>115.4888396619665</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09421107793841177</v>
+        <v>0.09058403876230803</v>
       </c>
       <c r="G19" t="n">
-        <v>0.477381564977969</v>
+        <v>0.4774025591513493</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1973496357002382</v>
+        <v>0.1897435131544623</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7163308766639734</v>
+        <v>0.7163476410339751</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6916524063842409</v>
+        <v>0.6916863352758773</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.607829955197645</v>
+        <v>2.602771568528715</v>
       </c>
       <c r="E20" t="n">
-        <v>125.4301115533643</v>
+        <v>124.0366106326403</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3097834881231069</v>
+        <v>-0.3112816237506828</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7718448307118235</v>
+        <v>0.7718747474579655</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4013546192146071</v>
+        <v>-0.403279968383257</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7317201405949403</v>
+        <v>0.7317371448978</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142308967331004</v>
+        <v>1.14235885514743</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>575.8765165020214</v>
+        <v>572.0687162309034</v>
       </c>
       <c r="E2" t="n">
-        <v>19712.32895053934</v>
+        <v>20113.11721357278</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6329023570826868</v>
+        <v>0.6163063061823193</v>
       </c>
       <c r="G2" t="n">
-        <v>0.494423815580008</v>
+        <v>0.4945746753153049</v>
       </c>
       <c r="H2" t="n">
-        <v>1.28008064567082</v>
+        <v>1.246133975196783</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>223.5303876133367</v>
+        <v>224.709019021551</v>
       </c>
       <c r="E3" t="n">
-        <v>6958.947030582772</v>
+        <v>6891.760590049061</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2510529355988753</v>
+        <v>0.2449116575911445</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5926547794660878</v>
+        <v>0.5927295028988143</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4236073753172875</v>
+        <v>0.4131929596778545</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8905822221340887</v>
+        <v>0.8906349846584236</v>
       </c>
       <c r="N3" t="n">
-        <v>1.0675210089468</v>
+        <v>1.067393172495794</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.68403686312427</v>
+        <v>37.63867018178777</v>
       </c>
       <c r="E4" t="n">
-        <v>865.3123586211194</v>
+        <v>632.6620821880289</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.314700357668753</v>
+        <v>-0.3158139052872779</v>
       </c>
       <c r="G4" t="n">
-        <v>0.55743499600059</v>
+        <v>0.5574661249090878</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5645507726042015</v>
+        <v>-0.5665167642944784</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7364848021760645</v>
+        <v>0.7366595301275717</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8303451205599856</v>
+        <v>0.8303351427683958</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.74464262082466</v>
+        <v>36.50266950187061</v>
       </c>
       <c r="E5" t="n">
-        <v>1230.899816112102</v>
+        <v>1241.108445979499</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7153067931177821</v>
+        <v>0.7029037870257449</v>
       </c>
       <c r="G5" t="n">
-        <v>1.098832110801617</v>
+        <v>1.09895845190409</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6509700490969027</v>
+        <v>0.6396090642079064</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4738235854311152</v>
+        <v>0.4740846438400798</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053049133395983</v>
+        <v>1.053429041699001</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.82802819255333</v>
+        <v>10.75724504536057</v>
       </c>
       <c r="E6" t="n">
-        <v>310.4939426577779</v>
+        <v>309.7047861823453</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4834649475966609</v>
+        <v>-0.4879051348277474</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8088005567740305</v>
+        <v>0.8089612623809135</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.5977554584346502</v>
+        <v>-0.6031254616466528</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6664464641587571</v>
+        <v>0.6666553230662879</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090202887252428</v>
+        <v>1.09042852098491</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.72052077786725</v>
+        <v>10.70554767193301</v>
       </c>
       <c r="E7" t="n">
-        <v>214.2874053646151</v>
+        <v>208.3429263631515</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.310903624973178</v>
+        <v>-0.3120977788340923</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7089534146337595</v>
+        <v>0.7089849427441731</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4385388638459252</v>
+        <v>-0.4402036771417136</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7502239380911327</v>
+        <v>0.7503760029751944</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075744747501198</v>
+        <v>1.075682427869566</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.584627089968258</v>
+        <v>9.514828217600428</v>
       </c>
       <c r="E8" t="n">
-        <v>394.8822984816207</v>
+        <v>400.7005334781725</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3417684303996634</v>
+        <v>-0.3498455260943723</v>
       </c>
       <c r="G8" t="n">
-        <v>1.162187350566213</v>
+        <v>1.16236739039581</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2940734385322256</v>
+        <v>-0.3009767212888196</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7371841901802245</v>
+        <v>0.737304804137193</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732817299384752</v>
+        <v>1.732840567634947</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.948698901289175</v>
+        <v>6.951364908446467</v>
       </c>
       <c r="E9" t="n">
-        <v>212.0888362041927</v>
+        <v>207.0593351831315</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3117872321026123</v>
+        <v>0.3124603801253447</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4807782622182382</v>
+        <v>0.480763304846309</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6485052603336788</v>
+        <v>0.6499256015914785</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.67330680851382</v>
+        <v>0.6737135499745679</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6547242813480518</v>
+        <v>0.6548995914500054</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.779343417309995</v>
+        <v>6.642824930537021</v>
       </c>
       <c r="E10" t="n">
-        <v>749.1763737277113</v>
+        <v>785.368553111696</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9864060648148931</v>
+        <v>0.9300235211972008</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8154727358407379</v>
+        <v>0.8165302763591654</v>
       </c>
       <c r="H10" t="n">
-        <v>1.209612561476903</v>
+        <v>1.138994533483916</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6638052325525937</v>
+        <v>0.6640279117062762</v>
       </c>
       <c r="N10" t="n">
-        <v>1.094840199839574</v>
+        <v>1.096293282526159</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.456358794273865</v>
+        <v>6.426458397953799</v>
       </c>
       <c r="E11" t="n">
-        <v>280.540205857912</v>
+        <v>277.0216355747838</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2952874271001634</v>
+        <v>-0.3008126682749631</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9509222794261714</v>
+        <v>0.9510477349380513</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3105274042778269</v>
+        <v>-0.3162960777090303</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.713389814307351</v>
+        <v>0.713531546103269</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372058236201172</v>
+        <v>1.372093223931719</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.249154143490162</v>
+        <v>6.310098527909635</v>
       </c>
       <c r="E12" t="n">
-        <v>113.684273135819</v>
+        <v>112.6215807282512</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2813957347757193</v>
+        <v>-0.2863812205657635</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6531982777944717</v>
+        <v>0.6533160364194983</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4307968106190572</v>
+        <v>-0.4383502081707303</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7889832050813537</v>
+        <v>0.7891082066690451</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042349608833733</v>
+        <v>1.042384642032975</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.696413371457807</v>
+        <v>4.617777520903357</v>
       </c>
       <c r="E13" t="n">
-        <v>239.993345015895</v>
+        <v>259.4281833412804</v>
       </c>
       <c r="F13" t="n">
-        <v>1.675679840000468</v>
+        <v>1.615530955822111</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8555094149172855</v>
+        <v>0.85620450820418</v>
       </c>
       <c r="H13" t="n">
-        <v>1.95869245946578</v>
+        <v>1.886851727994936</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6005980990366041</v>
+        <v>0.6009552362548894</v>
       </c>
       <c r="N13" t="n">
-        <v>1.039224471225118</v>
+        <v>1.040369853515671</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.421976541910248</v>
+        <v>4.399314897411571</v>
       </c>
       <c r="E14" t="n">
-        <v>104.1277652798429</v>
+        <v>106.0746880673286</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4205970364818402</v>
+        <v>-0.4242047093810741</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8430109239452438</v>
+        <v>0.8430858758662275</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.4989224036545929</v>
+        <v>-0.5031571771324309</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,45 +1192,45 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7599146512540426</v>
+        <v>0.7599732761556574</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295682635193638</v>
+        <v>1.295502513860299</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>XLM</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Stellar</t>
+          <t>Chainlink</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.101211921255932</v>
+        <v>4.100839505115551</v>
       </c>
       <c r="E15" t="n">
-        <v>147.5491930141609</v>
+        <v>198.919525955027</v>
       </c>
       <c r="F15" t="n">
-        <v>0.4885979610156619</v>
+        <v>-0.03766235297586351</v>
       </c>
       <c r="G15" t="n">
-        <v>0.9542116661005449</v>
+        <v>0.7883530409258271</v>
       </c>
       <c r="H15" t="n">
-        <v>0.5120435835922578</v>
+        <v>-0.04777346064604957</v>
       </c>
       <c r="I15" t="n">
-        <v>0.3858131487889274</v>
+        <v>0.4268646717284502</v>
       </c>
       <c r="J15" t="n">
         <v>275</v>
@@ -1246,45 +1246,45 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.5139669849049293</v>
+        <v>0.7129448967706198</v>
       </c>
       <c r="N15" t="n">
-        <v>0.9919289434136169</v>
+        <v>1.136435619198141</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>XLM</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Chainlink</t>
+          <t>Stellar</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.097146118200017</v>
+        <v>4.067262364179093</v>
       </c>
       <c r="E16" t="n">
-        <v>203.2867635221655</v>
+        <v>147.4248742946779</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.04084046317729484</v>
+        <v>0.4715216409689598</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7883656298825156</v>
+        <v>0.9545509653789023</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.05180396205676926</v>
+        <v>0.4939722006166455</v>
       </c>
       <c r="I16" t="n">
-        <v>0.4268646717284502</v>
+        <v>0.3858131487889274</v>
       </c>
       <c r="J16" t="n">
         <v>275</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.7131348773705052</v>
+        <v>0.5144228103398593</v>
       </c>
       <c r="N16" t="n">
-        <v>1.137103450669867</v>
+        <v>0.9928587425342541</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.796047122553254</v>
+        <v>3.713823058229553</v>
       </c>
       <c r="E17" t="n">
-        <v>117.8100073090976</v>
+        <v>124.8831496113272</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.07312087109618692</v>
+        <v>-0.1003468262054596</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7502857442426906</v>
+        <v>0.7513692978580185</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0974573642872454</v>
+        <v>-0.1335519384296449</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7209978936292685</v>
+        <v>0.721078594613899</v>
       </c>
       <c r="N17" t="n">
-        <v>1.094110809740132</v>
+        <v>1.095479296407731</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.092756201356205</v>
+        <v>3.080498765867759</v>
       </c>
       <c r="E18" t="n">
-        <v>74.43706215837071</v>
+        <v>73.81693280387736</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4655681066927082</v>
+        <v>-0.4691392422183018</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7395557727634073</v>
+        <v>0.7396180409710534</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6295239978359941</v>
+        <v>-0.6342993494349641</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.764547079168882</v>
+        <v>0.7645753253159134</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143604308957991</v>
+        <v>1.143393975691222</v>
       </c>
     </row>
     <row r="19">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.919436212642301</v>
+        <v>2.919599219384063</v>
       </c>
       <c r="E19" t="n">
-        <v>115.4888396619665</v>
+        <v>113.8525492578922</v>
       </c>
       <c r="F19" t="n">
         <v>0.09058403876230803</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7163476410339751</v>
+        <v>0.7163122431805278</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6916863352758773</v>
+        <v>0.6914411819161848</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.602771568528715</v>
+        <v>2.592955146223058</v>
       </c>
       <c r="E20" t="n">
-        <v>124.0366106326403</v>
+        <v>123.1550798667351</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3112816237506828</v>
+        <v>-0.3152727233435465</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7718747474579655</v>
+        <v>0.7719762504845297</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.403279968383257</v>
+        <v>-0.4083969204307336</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7317371448978</v>
+        <v>0.731891742477468</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14235885514743</v>
+        <v>1.142401888568475</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>572.0687162309034</v>
+        <v>573.0571963502723</v>
       </c>
       <c r="E2" t="n">
-        <v>20113.11721357278</v>
+        <v>20588.13225156335</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6163063061823193</v>
+        <v>0.6205798115731345</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4945746753153049</v>
+        <v>0.4945209689819553</v>
       </c>
       <c r="H2" t="n">
-        <v>1.246133975196783</v>
+        <v>1.254911015908365</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.709019021551</v>
+        <v>222.8950528098631</v>
       </c>
       <c r="E3" t="n">
-        <v>6891.760590049061</v>
+        <v>6956.268307861955</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2449116575911445</v>
+        <v>0.2461054587268476</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5927295028988143</v>
+        <v>0.592712631158261</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4131929596778545</v>
+        <v>0.4152188527616086</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906349846584236</v>
+        <v>0.8906301226134647</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067393172495794</v>
+        <v>1.067472880775443</v>
       </c>
     </row>
     <row r="4">
@@ -621,10 +621,10 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.63867018178777</v>
+        <v>37.64497009081798</v>
       </c>
       <c r="E4" t="n">
-        <v>632.6620821880289</v>
+        <v>592.2155281641458</v>
       </c>
       <c r="F4" t="n">
         <v>-0.3158139052872779</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7366595301275717</v>
+        <v>0.7366313552284365</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8303351427683958</v>
+        <v>0.8303935582976468</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.50266950187061</v>
+        <v>36.66983274762657</v>
       </c>
       <c r="E5" t="n">
-        <v>1241.108445979499</v>
+        <v>1220.193586269627</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7029037870257449</v>
+        <v>0.7123672339285523</v>
       </c>
       <c r="G5" t="n">
-        <v>1.09895845190409</v>
+        <v>1.098858923850988</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6396090642079064</v>
+        <v>0.6482790633687874</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4740846438400798</v>
+        <v>0.4739806456632896</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053429041699001</v>
+        <v>1.053216941016638</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.75724504536057</v>
+        <v>10.78158633324631</v>
       </c>
       <c r="E6" t="n">
-        <v>309.7047861823453</v>
+        <v>305.6690445611379</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4879051348277474</v>
+        <v>-0.4857750246038506</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8089612623809135</v>
+        <v>0.8088758600193284</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6031254616466528</v>
+        <v>-0.6005557201227921</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6666553230662879</v>
+        <v>0.6665838109999624</v>
       </c>
       <c r="N6" t="n">
-        <v>1.09042852098491</v>
+        <v>1.090314844500012</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.70554767193301</v>
+        <v>10.73939709879701</v>
       </c>
       <c r="E7" t="n">
-        <v>208.3429263631515</v>
+        <v>206.1656659014613</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3120977788340923</v>
+        <v>-0.3094102148415524</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7089849427441731</v>
+        <v>0.7089183176540668</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4402036771417136</v>
+        <v>-0.4364539709813738</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7503760029751944</v>
+        <v>0.7503249918927276</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075682427869566</v>
+        <v>1.075625027673605</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.514828217600428</v>
+        <v>9.523861908125173</v>
       </c>
       <c r="E8" t="n">
-        <v>400.7005334781725</v>
+        <v>396.475184393344</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3498455260943723</v>
+        <v>-0.3494789193475406</v>
       </c>
       <c r="G8" t="n">
-        <v>1.16236739039581</v>
+        <v>1.162357162863455</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3009767212888196</v>
+        <v>-0.3006639701747119</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.737304804137193</v>
+        <v>0.7372835213515458</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732840567634947</v>
+        <v>1.73296348558969</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.951364908446467</v>
+        <v>6.967528750371731</v>
       </c>
       <c r="E9" t="n">
-        <v>207.0593351831315</v>
+        <v>203.2685051860113</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3124603801253447</v>
+        <v>0.3158273969139811</v>
       </c>
       <c r="G9" t="n">
-        <v>0.480763304846309</v>
+        <v>0.4806944529590547</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6499256015914785</v>
+        <v>0.6570231775503411</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6737135499745679</v>
+        <v>0.673631184154593</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6548995914500054</v>
+        <v>0.6547968516481008</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.642824930537021</v>
+        <v>6.689114125700903</v>
       </c>
       <c r="E10" t="n">
-        <v>785.368553111696</v>
+        <v>808.8482429789619</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9300235211972008</v>
+        <v>0.9504799165106488</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8165302763591654</v>
+        <v>0.8160634237288784</v>
       </c>
       <c r="H10" t="n">
-        <v>1.138994533483916</v>
+        <v>1.164713291728692</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6640279117062762</v>
+        <v>0.6639811815656832</v>
       </c>
       <c r="N10" t="n">
-        <v>1.096293282526159</v>
+        <v>1.095708352742892</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.426458397953799</v>
+        <v>6.448462875012861</v>
       </c>
       <c r="E11" t="n">
-        <v>277.0216355747838</v>
+        <v>276.8436783197875</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3008126682749631</v>
+        <v>-0.2971753002705976</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9510477349380513</v>
+        <v>0.9509598417435869</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3162960777090303</v>
+        <v>-0.3125003677607732</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.713531546103269</v>
+        <v>0.7134737117181579</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372093223931719</v>
+        <v>1.372004203139192</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.310098527909635</v>
+        <v>6.339513088719244</v>
       </c>
       <c r="E12" t="n">
-        <v>112.6215807282512</v>
+        <v>110.0044205476218</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2863812205657635</v>
+        <v>-0.2826890896761974</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6533160364194983</v>
+        <v>0.653223637801895</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4383502081707303</v>
+        <v>-0.4327600431415027</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7891082066690451</v>
+        <v>0.7890494774764553</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042384642032975</v>
+        <v>1.042272830500868</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.617777520903357</v>
+        <v>4.634570468911763</v>
       </c>
       <c r="E13" t="n">
-        <v>259.4281833412804</v>
+        <v>258.854974684764</v>
       </c>
       <c r="F13" t="n">
-        <v>1.615530955822111</v>
+        <v>1.630170292212304</v>
       </c>
       <c r="G13" t="n">
-        <v>0.85620450820418</v>
+        <v>0.8559955674541838</v>
       </c>
       <c r="H13" t="n">
-        <v>1.886851727994936</v>
+        <v>1.9044144084304</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6009552362548894</v>
+        <v>0.6008331367112506</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040369853515671</v>
+        <v>1.040017580777633</v>
       </c>
     </row>
     <row r="14">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.399314897411571</v>
+        <v>4.402516596907467</v>
       </c>
       <c r="E14" t="n">
-        <v>106.0746880673286</v>
+        <v>106.7142312614824</v>
       </c>
       <c r="F14" t="n">
         <v>-0.4242047093810741</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7599732761556574</v>
+        <v>0.759977179655293</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295502513860299</v>
+        <v>1.29564986388152</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.100839505115551</v>
+        <v>4.093194146359115</v>
       </c>
       <c r="E15" t="n">
-        <v>198.919525955027</v>
+        <v>207.2013434001058</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.03766235297586351</v>
+        <v>-0.04184353812181951</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7883530409258271</v>
+        <v>0.788371738346709</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.04777346064604957</v>
+        <v>-0.05307589819184718</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7129448967706198</v>
+        <v>0.713095635188033</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136435619198141</v>
+        <v>1.13682630420704</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.067262364179093</v>
+        <v>4.077832740461086</v>
       </c>
       <c r="E16" t="n">
-        <v>147.4248742946779</v>
+        <v>146.5656819878349</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4715216409689598</v>
+        <v>0.4780837059046328</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9545509653789023</v>
+        <v>0.9544088677191367</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4939722006166455</v>
+        <v>0.5009212739684259</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5144228103398593</v>
+        <v>0.5142882307201252</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9928587425342541</v>
+        <v>0.9925590192329803</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.713823058229553</v>
+        <v>3.628394446219255</v>
       </c>
       <c r="E17" t="n">
-        <v>124.8831496113272</v>
+        <v>136.3327726847506</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1003468262054596</v>
+        <v>-0.1281086280520304</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7513692978580185</v>
+        <v>0.7533443792836172</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1335519384296449</v>
+        <v>-0.1700532075036567</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.721078594613899</v>
+        <v>0.7197265155149535</v>
       </c>
       <c r="N17" t="n">
-        <v>1.095479296407731</v>
+        <v>1.096418471800653</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.080498765867759</v>
+        <v>3.078946636468637</v>
       </c>
       <c r="E18" t="n">
-        <v>73.81693280387736</v>
+        <v>73.94554101734448</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4691392422183018</v>
+        <v>-0.4689806505111471</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7396180409710534</v>
+        <v>0.7396143298064289</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6342993494349641</v>
+        <v>-0.6340881072894954</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645753253159134</v>
+        <v>0.7645875382571081</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143393975691222</v>
+        <v>1.143530679498877</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.919599219384063</v>
+        <v>2.9275827511961</v>
       </c>
       <c r="E19" t="n">
-        <v>113.8525492578922</v>
+        <v>108.1079810480698</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09058403876230803</v>
+        <v>0.0923971871711089</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4774025591513493</v>
+        <v>0.4773899278649749</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1897435131544623</v>
+        <v>0.1935465785470919</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7163122431805278</v>
+        <v>0.7162974437013432</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6914411819161848</v>
+        <v>0.6914836911413716</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.592955146223058</v>
+        <v>2.594058553135173</v>
       </c>
       <c r="E20" t="n">
-        <v>123.1550798667351</v>
+        <v>123.9646782831953</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3152727233435465</v>
+        <v>-0.3147741487919842</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7719762504845297</v>
+        <v>0.7719618347512577</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4083969204307336</v>
+        <v>-0.4077586930102717</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.731891742477468</v>
+        <v>0.7318593202994411</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142401888568475</v>
+        <v>1.142454009263215</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>573.0571963502723</v>
+        <v>571.5800523826126</v>
       </c>
       <c r="E2" t="n">
-        <v>20588.13225156335</v>
+        <v>20591.95794765083</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6205798115731345</v>
+        <v>0.614540532887994</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4945209689819553</v>
+        <v>0.4945998826447435</v>
       </c>
       <c r="H2" t="n">
-        <v>1.254911015908365</v>
+        <v>1.24250036130599</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.8950528098631</v>
+        <v>224.4111092894967</v>
       </c>
       <c r="E3" t="n">
-        <v>6956.268307861955</v>
+        <v>6959.480965440793</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2461054587268476</v>
+        <v>0.2426584593075309</v>
       </c>
       <c r="G3" t="n">
-        <v>0.592712631158261</v>
+        <v>0.5927644367698066</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4152188527616086</v>
+        <v>0.4093674388258967</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906301226134647</v>
+        <v>0.8906501825684143</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067472880775443</v>
+        <v>1.06741989303766</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.64497009081798</v>
+        <v>37.70841357579117</v>
       </c>
       <c r="E4" t="n">
-        <v>592.2155281641458</v>
+        <v>584.3683862836144</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3158139052872779</v>
+        <v>-0.3143290759255474</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5574661249090878</v>
+        <v>0.5574253848399209</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5665167642944784</v>
+        <v>-0.563894441254797</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7366313552284365</v>
+        <v>0.7366278483028534</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8303935582976468</v>
+        <v>0.8301964400564841</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.66983274762657</v>
+        <v>36.49778377766535</v>
       </c>
       <c r="E5" t="n">
-        <v>1220.193586269627</v>
+        <v>1184.885609108518</v>
       </c>
       <c r="F5" t="n">
-        <v>0.7123672339285523</v>
+        <v>0.699643530268635</v>
       </c>
       <c r="G5" t="n">
-        <v>1.098858923850988</v>
+        <v>1.098997418116956</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6482790633687874</v>
+        <v>0.6366198125082203</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4739806456632896</v>
+        <v>0.4741288750826972</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053216941016638</v>
+        <v>1.053510985049803</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.78158633324631</v>
+        <v>10.75352196258366</v>
       </c>
       <c r="E6" t="n">
-        <v>305.6690445611379</v>
+        <v>300.5710252339964</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4857750246038506</v>
+        <v>-0.4880825455598102</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8088758600193284</v>
+        <v>0.8089690677330885</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.6005557201227921</v>
+        <v>-0.603338947096613</v>
       </c>
       <c r="I6" t="n">
         <v>0.5751178664414889</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6665838109999624</v>
+        <v>0.6666749719185763</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090314844500012</v>
+        <v>1.090415605499305</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.73939709879701</v>
+        <v>10.71770228513902</v>
       </c>
       <c r="E7" t="n">
-        <v>206.1656659014613</v>
+        <v>193.0440400649826</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3094102148415524</v>
+        <v>-0.3120977788340923</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7089183176540668</v>
+        <v>0.7089849427441731</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4364539709813738</v>
+        <v>-0.4402036771417136</v>
       </c>
       <c r="I7" t="n">
         <v>0.4277673545966229</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7503249918927276</v>
+        <v>0.7503800386132793</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075625027673605</v>
+        <v>1.075633390505133</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.523861908125173</v>
+        <v>9.494792825839486</v>
       </c>
       <c r="E8" t="n">
-        <v>396.475184393344</v>
+        <v>393.8136493848548</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3494789193475406</v>
+        <v>-0.3524103454802767</v>
       </c>
       <c r="G8" t="n">
-        <v>1.162357162863455</v>
+        <v>1.16244443223422</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3006639701747119</v>
+        <v>-0.303163175553212</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7372835213515458</v>
+        <v>0.7373394063255729</v>
       </c>
       <c r="N8" t="n">
-        <v>1.73296348558969</v>
+        <v>1.732948424829466</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.967528750371731</v>
+        <v>6.944569684170951</v>
       </c>
       <c r="E9" t="n">
-        <v>203.2685051860113</v>
+        <v>198.4242376348564</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3158273969139811</v>
+        <v>0.3095440205528994</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4806944529590547</v>
+        <v>0.4808309768834571</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6570231775503411</v>
+        <v>0.6437688822779947</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.673631184154593</v>
+        <v>0.67375815781798</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6547968516481008</v>
+        <v>0.6550017591482354</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.689114125700903</v>
+        <v>6.68324148798238</v>
       </c>
       <c r="E10" t="n">
-        <v>808.8482429789619</v>
+        <v>789.3960776540241</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9504799165106488</v>
+        <v>0.9470668263918389</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8160634237288784</v>
+        <v>0.8161347075834591</v>
       </c>
       <c r="H10" t="n">
-        <v>1.164713291728692</v>
+        <v>1.160429543789486</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6639811815656832</v>
+        <v>0.6641760665572124</v>
       </c>
       <c r="N10" t="n">
-        <v>1.095708352742892</v>
+        <v>1.095950805659503</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.448462875012861</v>
+        <v>6.45962390886993</v>
       </c>
       <c r="E11" t="n">
-        <v>276.8436783197875</v>
+        <v>279.3555199467607</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2971753002705976</v>
+        <v>-0.2960966685014832</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9509598417435869</v>
+        <v>0.950937707503057</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3125003677607732</v>
+        <v>-0.3113733593328261</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7134737117181579</v>
+        <v>0.713452051140915</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372004203139192</v>
+        <v>1.371711724429592</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.339513088719244</v>
+        <v>6.224939926447571</v>
       </c>
       <c r="E12" t="n">
-        <v>110.0044205476218</v>
+        <v>105.8265603461427</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2826890896761974</v>
+        <v>-0.2852740746785071</v>
       </c>
       <c r="G12" t="n">
-        <v>0.653223637801895</v>
+        <v>0.6532852152670734</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4327600431415027</v>
+        <v>-0.4366761530978204</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890494774764553</v>
+        <v>0.7890947976526944</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042272830500868</v>
+        <v>1.042264632159121</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.634570468911763</v>
+        <v>4.599597298163372</v>
       </c>
       <c r="E13" t="n">
-        <v>258.854974684764</v>
+        <v>260.2791008110123</v>
       </c>
       <c r="F13" t="n">
-        <v>1.630170292212304</v>
+        <v>1.597990389519667</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8559955674541838</v>
+        <v>0.8564887547123055</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9044144084304</v>
+        <v>1.865745908195177</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6008331367112506</v>
+        <v>0.6009975925805198</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040017580777633</v>
+        <v>1.040735547493267</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.402516596907467</v>
+        <v>4.39558948046078</v>
       </c>
       <c r="E14" t="n">
-        <v>106.7142312614824</v>
+        <v>106.8451245896541</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4242047093810741</v>
+        <v>-0.4266067340570521</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8430858758662275</v>
+        <v>0.8431545293502946</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5031571771324309</v>
+        <v>-0.5059650624017644</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.759977179655293</v>
+        <v>0.7600229200216355</v>
       </c>
       <c r="N14" t="n">
-        <v>1.29564986388152</v>
+        <v>1.295626606297759</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.093194146359115</v>
+        <v>4.108677316730721</v>
       </c>
       <c r="E15" t="n">
-        <v>207.2013434001058</v>
+        <v>203.8211609788614</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.04184353812181951</v>
+        <v>-0.03531892995217711</v>
       </c>
       <c r="G15" t="n">
-        <v>0.788371738346709</v>
+        <v>0.7883503347022257</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.05307589819184718</v>
+        <v>-0.04480105911988699</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.713095635188033</v>
+        <v>0.7128415906229959</v>
       </c>
       <c r="N15" t="n">
-        <v>1.13682630420704</v>
+        <v>1.136209138490539</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.077832740461086</v>
+        <v>4.037382770038113</v>
       </c>
       <c r="E16" t="n">
-        <v>146.5656819878349</v>
+        <v>145.0894107581974</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4780837059046328</v>
+        <v>0.4558021230361065</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9544088677191367</v>
+        <v>0.9549511043372064</v>
       </c>
       <c r="H16" t="n">
-        <v>0.5009212739684259</v>
+        <v>0.4773041477892845</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5142882307201252</v>
+        <v>0.514518282140391</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9925590192329803</v>
+        <v>0.9934086500472615</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.628394446219255</v>
+        <v>3.636943617421782</v>
       </c>
       <c r="E17" t="n">
-        <v>136.3327726847506</v>
+        <v>139.5721287786529</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1281086280520304</v>
+        <v>-0.1236811841487141</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7533443792836172</v>
+        <v>0.7529699120800279</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1700532075036567</v>
+        <v>-0.1642578038836283</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7197265155149535</v>
+        <v>0.7204227327710809</v>
       </c>
       <c r="N17" t="n">
-        <v>1.096418471800653</v>
+        <v>1.0967585330883</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.078946636468637</v>
+        <v>3.090641994486745</v>
       </c>
       <c r="E18" t="n">
-        <v>73.94554101734448</v>
+        <v>72.65600130681685</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4689806505111471</v>
+        <v>-0.4666797591423354</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7396143298064289</v>
+        <v>0.7395703824878364</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6340881072894954</v>
+        <v>-0.6310146676946069</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7645875382571081</v>
+        <v>0.7644640761758609</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143530679498877</v>
+        <v>1.143095680072541</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.9275827511961</v>
+        <v>2.927059089240554</v>
       </c>
       <c r="E19" t="n">
-        <v>108.1079810480698</v>
+        <v>107.364325524404</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0923971871711089</v>
+        <v>0.09058403876230803</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4773899278649749</v>
+        <v>0.4774025591513493</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1935465785470919</v>
+        <v>0.1897435131544623</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7162974437013432</v>
+        <v>0.716295244780256</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6914836911413716</v>
+        <v>0.6913895351885012</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.594058553135173</v>
+        <v>2.588302843661334</v>
       </c>
       <c r="E20" t="n">
-        <v>123.9646782831953</v>
+        <v>120.8974657980724</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3147741487919842</v>
+        <v>-0.3172661262372475</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7719618347512577</v>
+        <v>0.7720388490683006</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4077586930102717</v>
+        <v>-0.4109458048906807</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7318593202994411</v>
+        <v>0.7319293456089166</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142454009263215</v>
+        <v>1.142494993249121</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>571.5800523826126</v>
+        <v>569.4694196993096</v>
       </c>
       <c r="E2" t="n">
-        <v>20591.95794765083</v>
+        <v>21290.24716354195</v>
       </c>
       <c r="F2" t="n">
-        <v>0.614540532887994</v>
+        <v>0.6085461467842319</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4945998826447435</v>
+        <v>0.4946986329141468</v>
       </c>
       <c r="H2" t="n">
-        <v>1.24250036130599</v>
+        <v>1.230135088911481</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>224.4111092894967</v>
+        <v>222.9697224343552</v>
       </c>
       <c r="E3" t="n">
-        <v>6959.480965440793</v>
+        <v>7185.609353812661</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2426584593075309</v>
+        <v>0.2319939680654997</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5927644367698066</v>
+        <v>0.592984718045997</v>
       </c>
       <c r="H3" t="n">
-        <v>0.4093674388258967</v>
+        <v>0.3912309390197544</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8906501825684143</v>
+        <v>0.8907190497286654</v>
       </c>
       <c r="N3" t="n">
-        <v>1.06741989303766</v>
+        <v>1.067685959530871</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.70841357579117</v>
+        <v>37.36774563325673</v>
       </c>
       <c r="E4" t="n">
-        <v>584.3683862836144</v>
+        <v>595.1835061275435</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3143290759255474</v>
+        <v>-0.3228559848422849</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5574253848399209</v>
+        <v>0.5577431921292743</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.563894441254797</v>
+        <v>-0.5788613637931291</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7366278483028534</v>
+        <v>0.7368462674140248</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8301964400564841</v>
+        <v>0.8307502021485502</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.49778377766535</v>
+        <v>36.11674431011101</v>
       </c>
       <c r="E5" t="n">
-        <v>1184.885609108518</v>
+        <v>1221.911874209226</v>
       </c>
       <c r="F5" t="n">
-        <v>0.699643530268635</v>
+        <v>0.6797893964924362</v>
       </c>
       <c r="G5" t="n">
-        <v>1.098997418116956</v>
+        <v>1.099286689417615</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6366198125082203</v>
+        <v>0.6183913650883721</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,45 +706,45 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4741288750826972</v>
+        <v>0.474377005977608</v>
       </c>
       <c r="N5" t="n">
-        <v>1.053510985049803</v>
+        <v>1.054129309727575</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DOGE</t>
+          <t>ADA</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Dogecoin</t>
+          <t>Cardano</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.75352196258366</v>
+        <v>10.58746474672045</v>
       </c>
       <c r="E6" t="n">
-        <v>300.5710252339964</v>
+        <v>209.6071833886424</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4880825455598102</v>
+        <v>-0.3219300115438745</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8089690677330885</v>
+        <v>0.7093620161038456</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.603338947096613</v>
+        <v>-0.453830349293394</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5751178664414889</v>
+        <v>0.4277673545966229</v>
       </c>
       <c r="J6" t="n">
         <v>275</v>
@@ -760,45 +760,45 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.6666749719185763</v>
+        <v>0.7505644122932073</v>
       </c>
       <c r="N6" t="n">
-        <v>1.090415605499305</v>
+        <v>1.076255015268068</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADA</t>
+          <t>DOGE</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Cardano</t>
+          <t>Dogecoin</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.71770228513902</v>
+        <v>10.53402150849116</v>
       </c>
       <c r="E7" t="n">
-        <v>193.0440400649826</v>
+        <v>341.0167010773678</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3120977788340923</v>
+        <v>-0.5008161133281084</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7089849427441731</v>
+        <v>0.8098091398956024</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.4402036771417136</v>
+        <v>-0.6184372201487769</v>
       </c>
       <c r="I7" t="n">
-        <v>0.4277673545966229</v>
+        <v>0.5751178664414889</v>
       </c>
       <c r="J7" t="n">
         <v>275</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.7503800386132793</v>
+        <v>0.6669167817367844</v>
       </c>
       <c r="N7" t="n">
-        <v>1.075633390505133</v>
+        <v>1.091725890202605</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.494792825839486</v>
+        <v>9.379444689538746</v>
       </c>
       <c r="E8" t="n">
-        <v>393.8136493848548</v>
+        <v>400.8903225443714</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.3524103454802767</v>
+        <v>-0.361184983870468</v>
       </c>
       <c r="G8" t="n">
-        <v>1.16244443223422</v>
+        <v>1.16278094686732</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.303163175553212</v>
+        <v>-0.3106216909070849</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7373394063255729</v>
+        <v>0.7374736120042367</v>
       </c>
       <c r="N8" t="n">
-        <v>1.732948424829466</v>
+        <v>1.733419516048608</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.944569684170951</v>
+        <v>6.853593202073926</v>
       </c>
       <c r="E9" t="n">
-        <v>198.4242376348564</v>
+        <v>214.424467405769</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3095440205528994</v>
+        <v>0.2864942060628595</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4808309768834571</v>
+        <v>0.4816293133323927</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6437688822779947</v>
+        <v>0.5948437898860565</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.67375815781798</v>
+        <v>0.6738174396442838</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6550017591482354</v>
+        <v>0.6560160250606321</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.68324148798238</v>
+        <v>6.555210122200329</v>
       </c>
       <c r="E10" t="n">
-        <v>789.3960776540241</v>
+        <v>812.3008204399295</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9470668263918389</v>
+        <v>0.9050937035220539</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8161347075834591</v>
+        <v>0.8172283120930758</v>
       </c>
       <c r="H10" t="n">
-        <v>1.160429543789486</v>
+        <v>1.107516333108845</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6641760665572124</v>
+        <v>0.6642305438234747</v>
       </c>
       <c r="N10" t="n">
-        <v>1.095950805659503</v>
+        <v>1.097290289588752</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.45962390886993</v>
+        <v>6.377257457675924</v>
       </c>
       <c r="E11" t="n">
-        <v>279.3555199467607</v>
+        <v>285.4027183331055</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.2960966685014832</v>
+        <v>-0.3056552414448989</v>
       </c>
       <c r="G11" t="n">
-        <v>0.950937707503057</v>
+        <v>0.9511965740286774</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3113733593328261</v>
+        <v>-0.3213376181017277</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.713452051140915</v>
+        <v>0.7136378387354293</v>
       </c>
       <c r="N11" t="n">
-        <v>1.371711724429592</v>
+        <v>1.372168472153783</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.224939926447571</v>
+        <v>6.143579462292563</v>
       </c>
       <c r="E12" t="n">
-        <v>105.8265603461427</v>
+        <v>111.4304267443246</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2852740746785071</v>
+        <v>-0.296694121217328</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6532852152670734</v>
+        <v>0.6537318105027087</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4366761530978204</v>
+        <v>-0.4538468473626444</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7890947976526944</v>
+        <v>0.7892575234433373</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042264632159121</v>
+        <v>1.042983981407203</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.599597298163372</v>
+        <v>4.553513630584949</v>
       </c>
       <c r="E13" t="n">
-        <v>260.2791008110123</v>
+        <v>273.0326070478782</v>
       </c>
       <c r="F13" t="n">
-        <v>1.597990389519667</v>
+        <v>1.573191181484776</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8564887547123055</v>
+        <v>0.8569539601195821</v>
       </c>
       <c r="H13" t="n">
-        <v>1.865745908195177</v>
+        <v>1.83579428382039</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6009975925805198</v>
+        <v>0.6012153834672369</v>
       </c>
       <c r="N13" t="n">
-        <v>1.040735547493267</v>
+        <v>1.041470239592264</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.39558948046078</v>
+        <v>4.351726329355177</v>
       </c>
       <c r="E14" t="n">
-        <v>106.8451245896541</v>
+        <v>111.0669278680487</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4266067340570521</v>
+        <v>-0.4326009403773545</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8431545293502946</v>
+        <v>0.8433915343720362</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5059650624017644</v>
+        <v>-0.5129301430556285</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7600229200216355</v>
+        <v>0.7601566316598218</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295626606297759</v>
+        <v>1.295960055846603</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.108677316730721</v>
+        <v>4.016455908164319</v>
       </c>
       <c r="E15" t="n">
-        <v>203.8211609788614</v>
+        <v>249.320460830136</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.03531892995217711</v>
+        <v>-0.06351302964227057</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7883503347022257</v>
+        <v>0.7887554092083425</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.04480105911988699</v>
+        <v>-0.08052309867011534</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7128415906229959</v>
+        <v>0.7134355354609948</v>
       </c>
       <c r="N15" t="n">
-        <v>1.136209138490539</v>
+        <v>1.13751302363912</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>4.037382770038113</v>
+        <v>3.974061255577073</v>
       </c>
       <c r="E16" t="n">
-        <v>145.0894107581974</v>
+        <v>145.4605682688363</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4558021230361065</v>
+        <v>0.4296958004891203</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9549511043372064</v>
+        <v>0.9558031737705821</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4773041477892845</v>
+        <v>0.4495651534551804</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.514518282140391</v>
+        <v>0.514808795724903</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9934086500472615</v>
+        <v>0.994657854500819</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.636943617421782</v>
+        <v>3.627188913063383</v>
       </c>
       <c r="E17" t="n">
-        <v>139.5721287786529</v>
+        <v>141.4028296183255</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1236811841487141</v>
+        <v>-0.1271867000183446</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7529699120800279</v>
+        <v>0.7532645339927242</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1642578038836283</v>
+        <v>-0.1688473229241046</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7204227327710809</v>
+        <v>0.7207120044579566</v>
       </c>
       <c r="N17" t="n">
-        <v>1.0967585330883</v>
+        <v>1.097409121555428</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.090641994486745</v>
+        <v>3.056370183275027</v>
       </c>
       <c r="E18" t="n">
-        <v>72.65600130681685</v>
+        <v>75.17451019324885</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4666797591423354</v>
+        <v>-0.4741288923025596</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7395703824878364</v>
+        <v>0.7397798647100881</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6310146676946069</v>
+        <v>-0.6409053759368887</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7644640761758609</v>
+        <v>0.7647115490742604</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143095680072541</v>
+        <v>1.143561288989001</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.927059089240554</v>
+        <v>2.922399111251607</v>
       </c>
       <c r="E19" t="n">
-        <v>107.364325524404</v>
+        <v>97.70838946080242</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09058403876230803</v>
+        <v>0.09421107793841177</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4774025591513493</v>
+        <v>0.477381564977969</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1897435131544623</v>
+        <v>0.1973496357002382</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.716295244780256</v>
+        <v>0.7160444943477136</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6913895351885012</v>
+        <v>0.6909791508659633</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.588302843661334</v>
+        <v>2.569218520585752</v>
       </c>
       <c r="E20" t="n">
-        <v>120.8974657980724</v>
+        <v>123.9436348465668</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3172661262372475</v>
+        <v>-0.322740583274319</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7720388490683006</v>
+        <v>0.7722517000480853</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4109458048906807</v>
+        <v>-0.4179214927648888</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7319293456089166</v>
+        <v>0.7320563132467457</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142494993249121</v>
+        <v>1.14278005804363</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>569.4694196993096</v>
+        <v>567.2247447603904</v>
       </c>
       <c r="E2" t="n">
-        <v>21290.24716354195</v>
+        <v>21592.13807839657</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6085461467842319</v>
+        <v>0.6003449487536134</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4946986329141468</v>
+        <v>0.4948667795964904</v>
       </c>
       <c r="H2" t="n">
-        <v>1.230135088911481</v>
+        <v>1.213144574471394</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.9697224343552</v>
+        <v>222.3062585300183</v>
       </c>
       <c r="E3" t="n">
-        <v>7185.609353812661</v>
+        <v>7274.02405489712</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2319939680654997</v>
+        <v>0.2269853259724774</v>
       </c>
       <c r="G3" t="n">
-        <v>0.592984718045997</v>
+        <v>0.5931195724723533</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3912309390197544</v>
+        <v>0.3826974129791642</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907190497286654</v>
+        <v>0.8907822277681158</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067685959530871</v>
+        <v>1.067641627774244</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>37.36774563325673</v>
+        <v>36.950497156719</v>
       </c>
       <c r="E4" t="n">
-        <v>595.1835061275435</v>
+        <v>689.5529118408518</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3228559848422849</v>
+        <v>-0.3313564992861905</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5577431921292743</v>
+        <v>0.5582630333807393</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5788613637931291</v>
+        <v>-0.593549061057394</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.7368462674140248</v>
+        <v>0.737076106665165</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8307502021485502</v>
+        <v>0.8315012445872383</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.11674431011101</v>
+        <v>36.03650005874329</v>
       </c>
       <c r="E5" t="n">
-        <v>1221.911874209226</v>
+        <v>1237.938132133535</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6797893964924362</v>
+        <v>0.677839641832543</v>
       </c>
       <c r="G5" t="n">
-        <v>1.099286689417615</v>
+        <v>1.099319928124007</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6183913650883721</v>
+        <v>0.6165990668333272</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.474377005977608</v>
+        <v>0.4745358672930295</v>
       </c>
       <c r="N5" t="n">
-        <v>1.054129309727575</v>
+        <v>1.054155900200451</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.58746474672045</v>
+        <v>10.55477504474717</v>
       </c>
       <c r="E6" t="n">
-        <v>209.6071833886424</v>
+        <v>218.606957294159</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3219300115438745</v>
+        <v>-0.3249025718854512</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7093620161038456</v>
+        <v>0.7095174409106647</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.453830349293394</v>
+        <v>-0.4579204867303039</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7505644122932073</v>
+        <v>0.7507159659221599</v>
       </c>
       <c r="N6" t="n">
-        <v>1.076255015268068</v>
+        <v>1.076342346977066</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.53402150849116</v>
+        <v>10.48239246667142</v>
       </c>
       <c r="E7" t="n">
-        <v>341.0167010773678</v>
+        <v>360.012925944667</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5008161133281084</v>
+        <v>-0.5046910967717225</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8098091398956024</v>
+        <v>0.8101750864622204</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6184372201487769</v>
+        <v>-0.6229407756483227</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6669167817367844</v>
+        <v>0.6671951365559486</v>
       </c>
       <c r="N7" t="n">
-        <v>1.091725890202605</v>
+        <v>1.09230382748089</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.379444689538746</v>
+        <v>9.338734426281485</v>
       </c>
       <c r="E8" t="n">
-        <v>400.8903225443714</v>
+        <v>421.4215703408025</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.361184983870468</v>
+        <v>-0.364467848138569</v>
       </c>
       <c r="G8" t="n">
-        <v>1.16278094686732</v>
+        <v>1.162936015936013</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3106216909070849</v>
+        <v>-0.3134031822423347</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7374736120042367</v>
+        <v>0.7375849516209149</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733419516048608</v>
+        <v>1.733323270864527</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.853593202073926</v>
+        <v>6.857389856822039</v>
       </c>
       <c r="E9" t="n">
-        <v>214.424467405769</v>
+        <v>215.8011427787857</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2864942060628595</v>
+        <v>0.2905150441063309</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4816293133323927</v>
+        <v>0.4814562772630375</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5948437898860565</v>
+        <v>0.6034089860824718</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6738174396442838</v>
+        <v>0.6741996314337804</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6560160250606321</v>
+        <v>0.6559293492016046</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.555210122200329</v>
+        <v>6.41004691461774</v>
       </c>
       <c r="E10" t="n">
-        <v>812.3008204399295</v>
+        <v>884.5659363938699</v>
       </c>
       <c r="F10" t="n">
-        <v>0.9050937035220539</v>
+        <v>0.8358306068460006</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8172283120930758</v>
+        <v>0.8199200946571775</v>
       </c>
       <c r="H10" t="n">
-        <v>1.107516333108845</v>
+        <v>1.019404954571184</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6642305438234747</v>
+        <v>0.6640270877059714</v>
       </c>
       <c r="N10" t="n">
-        <v>1.097290289588752</v>
+        <v>1.100193375378215</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.377257457675924</v>
+        <v>6.365064016898481</v>
       </c>
       <c r="E11" t="n">
-        <v>285.4027183331055</v>
+        <v>290.3592741303761</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3056552414448989</v>
+        <v>-0.3096843697581836</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9511965740286774</v>
+        <v>0.9513482247309806</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3213376181017277</v>
+        <v>-0.3255215721307045</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7136378387354293</v>
+        <v>0.7137527236347843</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372168472153783</v>
+        <v>1.372141785473105</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.143579462292563</v>
+        <v>6.126287270641353</v>
       </c>
       <c r="E12" t="n">
-        <v>111.4304267443246</v>
+        <v>113.6157778153424</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.296694121217328</v>
+        <v>-0.2992665517904652</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6537318105027087</v>
+        <v>0.6538718822774451</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4538468473626444</v>
+        <v>-0.4576837755251313</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.7892575234433373</v>
+        <v>0.789401900539029</v>
       </c>
       <c r="N12" t="n">
-        <v>1.042983981407203</v>
+        <v>1.043043760180721</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.553513630584949</v>
+        <v>4.417123889892712</v>
       </c>
       <c r="E13" t="n">
-        <v>273.0326070478782</v>
+        <v>311.9217844106036</v>
       </c>
       <c r="F13" t="n">
-        <v>1.573191181484776</v>
+        <v>1.458723875661013</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8569539601195821</v>
+        <v>0.8600737909048169</v>
       </c>
       <c r="H13" t="n">
-        <v>1.83579428382039</v>
+        <v>1.696045026702189</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.6012153834672369</v>
+        <v>0.601232539086341</v>
       </c>
       <c r="N13" t="n">
-        <v>1.041470239592264</v>
+        <v>1.044936476699769</v>
       </c>
     </row>
     <row r="14">
@@ -1161,19 +1161,19 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.351726329355177</v>
+        <v>4.338027406240505</v>
       </c>
       <c r="E14" t="n">
-        <v>111.0669278680487</v>
+        <v>116.1156298033981</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.4326009403773545</v>
+        <v>-0.43439616913862</v>
       </c>
       <c r="G14" t="n">
-        <v>0.8433915343720362</v>
+        <v>0.8434808378451875</v>
       </c>
       <c r="H14" t="n">
-        <v>-0.5129301430556285</v>
+        <v>-0.5150041941063622</v>
       </c>
       <c r="I14" t="n">
         <v>0.4691011235955056</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7601566316598218</v>
+        <v>0.7602342816945529</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295960055846603</v>
+        <v>1.295789241308982</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>4.016455908164319</v>
+        <v>3.98442057665563</v>
       </c>
       <c r="E15" t="n">
-        <v>249.320460830136</v>
+        <v>261.4651252768815</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.06351302964227057</v>
+        <v>-0.07397026144663799</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7887554092083425</v>
+        <v>0.7891140356259425</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.08052309867011534</v>
+        <v>-0.09373836746923803</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7134355354609948</v>
+        <v>0.7136654118197158</v>
       </c>
       <c r="N15" t="n">
-        <v>1.13751302363912</v>
+        <v>1.138010099742206</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.974061255577073</v>
+        <v>3.983309065948726</v>
       </c>
       <c r="E16" t="n">
-        <v>145.4605682688363</v>
+        <v>145.0056424801584</v>
       </c>
       <c r="F16" t="n">
-        <v>0.4296958004891203</v>
+        <v>0.432301184638789</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9558031737705821</v>
+        <v>0.9557075642163176</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4495651534551804</v>
+        <v>0.4523362593590822</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.514808795724903</v>
+        <v>0.5151882364934369</v>
       </c>
       <c r="N16" t="n">
-        <v>0.994657854500819</v>
+        <v>0.9949532175376896</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.627188913063383</v>
+        <v>3.594954591071653</v>
       </c>
       <c r="E17" t="n">
-        <v>141.4028296183255</v>
+        <v>132.6720488156938</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1271867000183446</v>
+        <v>-0.1400717773887407</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7532645339927242</v>
+        <v>0.7544699074138658</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1688473229241046</v>
+        <v>-0.1856558837036612</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7207120044579566</v>
+        <v>0.7208128820819394</v>
       </c>
       <c r="N17" t="n">
-        <v>1.097409121555428</v>
+        <v>1.098945515903326</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.056370183275027</v>
+        <v>3.040017613122969</v>
       </c>
       <c r="E18" t="n">
-        <v>75.17451019324885</v>
+        <v>77.83183368294932</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4741288923025596</v>
+        <v>-0.4777647755251542</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7397798647100881</v>
+        <v>0.7399530020023869</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6409053759368887</v>
+        <v>-0.6456690819988227</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7647115490742604</v>
+        <v>0.7648387118577219</v>
       </c>
       <c r="N18" t="n">
-        <v>1.143561288989001</v>
+        <v>1.14363041574184</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.922399111251607</v>
+        <v>2.921473064074863</v>
       </c>
       <c r="E19" t="n">
-        <v>97.70838946080242</v>
+        <v>80.1932237133428</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09421107793841177</v>
+        <v>0.09058403876230803</v>
       </c>
       <c r="G19" t="n">
-        <v>0.477381564977969</v>
+        <v>0.4774025591513493</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1973496357002382</v>
+        <v>0.1897435131544623</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7160444943477136</v>
+        <v>0.7160658665975727</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6909791508659633</v>
+        <v>0.6907953641853926</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.569218520585752</v>
+        <v>2.568011725512398</v>
       </c>
       <c r="E20" t="n">
-        <v>123.9436348465668</v>
+        <v>124.352301980703</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.322740583274319</v>
+        <v>-0.3237347704403523</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7722517000480853</v>
+        <v>0.7722968116304642</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4179214927648888</v>
+        <v>-0.4191843933123162</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7320563132467457</v>
+        <v>0.7321471267324663</v>
       </c>
       <c r="N20" t="n">
-        <v>1.14278005804363</v>
+        <v>1.142600220772425</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
+++ b/tame_output/MOZAIC/data/universe_last2023-08-02.xlsx
@@ -513,19 +513,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>567.2247447603904</v>
+        <v>567.0531729134457</v>
       </c>
       <c r="E2" t="n">
-        <v>21592.13807839657</v>
+        <v>21100.2484523187</v>
       </c>
       <c r="F2" t="n">
-        <v>0.6003449487536134</v>
+        <v>0.599013994545736</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4948667795964904</v>
+        <v>0.4948976748481076</v>
       </c>
       <c r="H2" t="n">
-        <v>1.213144574471394</v>
+        <v>1.210379488506555</v>
       </c>
       <c r="I2" t="n">
         <v>0.2590724514387045</v>
@@ -567,19 +567,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>222.3062585300183</v>
+        <v>220.8287123170521</v>
       </c>
       <c r="E3" t="n">
-        <v>7274.02405489712</v>
+        <v>7025.460931762622</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2269853259724774</v>
+        <v>0.2312654487494212</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5931195724723533</v>
+        <v>0.5930030835068475</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3826974129791642</v>
+        <v>0.3899902971528997</v>
       </c>
       <c r="I3" t="n">
         <v>0.3295577524045769</v>
@@ -598,10 +598,10 @@
         </is>
       </c>
       <c r="M3" t="n">
-        <v>0.8907822277681158</v>
+        <v>0.8907403803704195</v>
       </c>
       <c r="N3" t="n">
-        <v>1.067641627774244</v>
+        <v>1.067315162322874</v>
       </c>
     </row>
     <row r="4">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>36.950497156719</v>
+        <v>37.0284407472905</v>
       </c>
       <c r="E4" t="n">
-        <v>689.5529118408518</v>
+        <v>675.3647282600442</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.3313564992861905</v>
+        <v>-0.330618376186314</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5582630333807393</v>
+        <v>0.5582098223213247</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.593549061057394</v>
+        <v>-0.5922833367772571</v>
       </c>
       <c r="I4" t="n">
         <v>0.3496897913141569</v>
@@ -652,10 +652,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.737076106665165</v>
+        <v>0.7371098468930423</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8315012445872383</v>
+        <v>0.8314081426867653</v>
       </c>
     </row>
     <row r="5">
@@ -675,19 +675,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>36.03650005874329</v>
+        <v>36.13624171078176</v>
       </c>
       <c r="E5" t="n">
-        <v>1237.938132133535</v>
+        <v>1203.196645386879</v>
       </c>
       <c r="F5" t="n">
-        <v>0.677839641832543</v>
+        <v>0.6814146184485432</v>
       </c>
       <c r="G5" t="n">
-        <v>1.099319928124007</v>
+        <v>1.099259645097609</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6165990668333272</v>
+        <v>0.6198850485301285</v>
       </c>
       <c r="I5" t="n">
         <v>0.3422195892575038</v>
@@ -706,10 +706,10 @@
         </is>
       </c>
       <c r="M5" t="n">
-        <v>0.4745358672930295</v>
+        <v>0.4745094976477587</v>
       </c>
       <c r="N5" t="n">
-        <v>1.054155900200451</v>
+        <v>1.053973717172566</v>
       </c>
     </row>
     <row r="6">
@@ -729,19 +729,19 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>10.55477504474717</v>
+        <v>10.55004515112539</v>
       </c>
       <c r="E6" t="n">
-        <v>218.606957294159</v>
+        <v>214.632978178252</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3249025718854512</v>
+        <v>-0.3251996507267755</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7095174409106647</v>
+        <v>0.7095340354106313</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4579204867303039</v>
+        <v>-0.4583284726272102</v>
       </c>
       <c r="I6" t="n">
         <v>0.4277673545966229</v>
@@ -760,10 +760,10 @@
         </is>
       </c>
       <c r="M6" t="n">
-        <v>0.7507159659221599</v>
+        <v>0.7507384182596166</v>
       </c>
       <c r="N6" t="n">
-        <v>1.076342346977066</v>
+        <v>1.076332515825674</v>
       </c>
     </row>
     <row r="7">
@@ -783,19 +783,19 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>10.48239246667142</v>
+        <v>10.4824738940748</v>
       </c>
       <c r="E7" t="n">
-        <v>360.012925944667</v>
+        <v>362.9504480778944</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.5046910967717225</v>
+        <v>-0.5047790779817274</v>
       </c>
       <c r="G7" t="n">
-        <v>0.8101750864622204</v>
+        <v>0.8101839967743365</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6229407756483227</v>
+        <v>-0.623042518725935</v>
       </c>
       <c r="I7" t="n">
         <v>0.5751178664414889</v>
@@ -814,10 +814,10 @@
         </is>
       </c>
       <c r="M7" t="n">
-        <v>0.6671951365559486</v>
+        <v>0.6672407469777577</v>
       </c>
       <c r="N7" t="n">
-        <v>1.09230382748089</v>
+        <v>1.092322317665058</v>
       </c>
     </row>
     <row r="8">
@@ -837,19 +837,19 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>9.338734426281485</v>
+        <v>9.363728726382696</v>
       </c>
       <c r="E8" t="n">
-        <v>421.4215703408025</v>
+        <v>411.3434313024516</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.364467848138569</v>
+        <v>-0.3630093122663313</v>
       </c>
       <c r="G8" t="n">
-        <v>1.162936015936013</v>
+        <v>1.162865152602194</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.3134031822423347</v>
+        <v>-0.3121680200442926</v>
       </c>
       <c r="I8" t="n">
         <v>0.7387533875338753</v>
@@ -868,10 +868,10 @@
         </is>
       </c>
       <c r="M8" t="n">
-        <v>0.7375849516209149</v>
+        <v>0.7375651602138324</v>
       </c>
       <c r="N8" t="n">
-        <v>1.733323270864527</v>
+        <v>1.733062946495675</v>
       </c>
     </row>
     <row r="9">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>6.857389856822039</v>
+        <v>6.8704041372744</v>
       </c>
       <c r="E9" t="n">
-        <v>215.8011427787857</v>
+        <v>214.5563457669391</v>
       </c>
       <c r="F9" t="n">
-        <v>0.2905150441063309</v>
+        <v>0.2927501791181775</v>
       </c>
       <c r="G9" t="n">
-        <v>0.4814562772630375</v>
+        <v>0.4813662726633978</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6034089860824718</v>
+        <v>0.6081651244454495</v>
       </c>
       <c r="I9" t="n">
         <v>0.2154834665412946</v>
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.6741996314337804</v>
+        <v>0.6742392836920252</v>
       </c>
       <c r="N9" t="n">
-        <v>0.6559293492016046</v>
+        <v>0.6558043558674653</v>
       </c>
     </row>
     <row r="10">
@@ -945,19 +945,19 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>6.41004691461774</v>
+        <v>6.444796399888882</v>
       </c>
       <c r="E10" t="n">
-        <v>884.5659363938699</v>
+        <v>910.0128048625576</v>
       </c>
       <c r="F10" t="n">
-        <v>0.8358306068460006</v>
+        <v>0.8577235216205332</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8199200946571775</v>
+        <v>0.8189488867452294</v>
       </c>
       <c r="H10" t="n">
-        <v>1.019404954571184</v>
+        <v>1.047346831411429</v>
       </c>
       <c r="I10" t="n">
         <v>0.3268819295856837</v>
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="M10" t="n">
-        <v>0.6640270877059714</v>
+        <v>0.6644102919637406</v>
       </c>
       <c r="N10" t="n">
-        <v>1.100193375378215</v>
+        <v>1.099455698822543</v>
       </c>
     </row>
     <row r="11">
@@ -999,19 +999,19 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>6.365064016898481</v>
+        <v>6.358467038063648</v>
       </c>
       <c r="E11" t="n">
-        <v>290.3592741303761</v>
+        <v>287.3923926270877</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.3096843697581836</v>
+        <v>-0.3091474868269746</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9513482247309806</v>
+        <v>0.9513265544397939</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3255215721307045</v>
+        <v>-0.3249646353128677</v>
       </c>
       <c r="I11" t="n">
         <v>0.6126386245816655</v>
@@ -1030,10 +1030,10 @@
         </is>
       </c>
       <c r="M11" t="n">
-        <v>0.7137527236347843</v>
+        <v>0.7137417379669261</v>
       </c>
       <c r="N11" t="n">
-        <v>1.372141785473105</v>
+        <v>1.372003755217364</v>
       </c>
     </row>
     <row r="12">
@@ -1053,19 +1053,19 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>6.126287270641353</v>
+        <v>6.131802551723884</v>
       </c>
       <c r="E12" t="n">
-        <v>113.6157778153424</v>
+        <v>112.1620759550909</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.2992665517904652</v>
+        <v>-0.2996338520598202</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6538718822774451</v>
+        <v>0.6538930710587328</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4576837755251313</v>
+        <v>-0.4582306577659193</v>
       </c>
       <c r="I12" t="n">
         <v>0.4207389749702026</v>
@@ -1084,10 +1084,10 @@
         </is>
       </c>
       <c r="M12" t="n">
-        <v>0.789401900539029</v>
+        <v>0.789425174676745</v>
       </c>
       <c r="N12" t="n">
-        <v>1.043043760180721</v>
+        <v>1.043043194734919</v>
       </c>
     </row>
     <row r="13">
@@ -1107,19 +1107,19 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>4.417123889892712</v>
+        <v>4.439500728016951</v>
       </c>
       <c r="E13" t="n">
-        <v>311.9217844106036</v>
+        <v>313.30042449179</v>
       </c>
       <c r="F13" t="n">
-        <v>1.458723875661013</v>
+        <v>1.481803175937424</v>
       </c>
       <c r="G13" t="n">
-        <v>0.8600737909048169</v>
+        <v>0.8593150415634334</v>
       </c>
       <c r="H13" t="n">
-        <v>1.696045026702189</v>
+        <v>1.724400370371079</v>
       </c>
       <c r="I13" t="n">
         <v>0.3000688231245698</v>
@@ -1138,10 +1138,10 @@
         </is>
       </c>
       <c r="M13" t="n">
-        <v>0.601232539086341</v>
+        <v>0.6014896141590517</v>
       </c>
       <c r="N13" t="n">
-        <v>1.044936476699769</v>
+        <v>1.044395839907097</v>
       </c>
     </row>
     <row r="14">
@@ -1161,10 +1161,10 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>4.338027406240505</v>
+        <v>4.33877897172359</v>
       </c>
       <c r="E14" t="n">
-        <v>116.1156298033981</v>
+        <v>115.7574240937668</v>
       </c>
       <c r="F14" t="n">
         <v>-0.43439616913862</v>
@@ -1192,10 +1192,10 @@
         </is>
       </c>
       <c r="M14" t="n">
-        <v>0.7602342816945529</v>
+        <v>0.7602368307519998</v>
       </c>
       <c r="N14" t="n">
-        <v>1.295789241308982</v>
+        <v>1.29571269285166</v>
       </c>
     </row>
     <row r="15">
@@ -1215,19 +1215,19 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>3.98442057665563</v>
+        <v>3.985465787945506</v>
       </c>
       <c r="E15" t="n">
-        <v>261.4651252768815</v>
+        <v>259.9409125691319</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.07397026144663799</v>
+        <v>-0.07513038670069183</v>
       </c>
       <c r="G15" t="n">
-        <v>0.7891140356259425</v>
+        <v>0.7891608339494625</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.09373836746923803</v>
+        <v>-0.0952028832002364</v>
       </c>
       <c r="I15" t="n">
         <v>0.4268646717284502</v>
@@ -1246,10 +1246,10 @@
         </is>
       </c>
       <c r="M15" t="n">
-        <v>0.7136654118197158</v>
+        <v>0.713700344177667</v>
       </c>
       <c r="N15" t="n">
-        <v>1.138010099742206</v>
+        <v>1.138062244835014</v>
       </c>
     </row>
     <row r="16">
@@ -1269,19 +1269,19 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>3.983309065948726</v>
+        <v>3.983398282747706</v>
       </c>
       <c r="E16" t="n">
-        <v>145.0056424801584</v>
+        <v>140.1930802774644</v>
       </c>
       <c r="F16" t="n">
-        <v>0.432301184638789</v>
+        <v>0.4296958004891203</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9557075642163176</v>
+        <v>0.9558031737705821</v>
       </c>
       <c r="H16" t="n">
-        <v>0.4523362593590822</v>
+        <v>0.4495651534551804</v>
       </c>
       <c r="I16" t="n">
         <v>0.3858131487889274</v>
@@ -1300,10 +1300,10 @@
         </is>
       </c>
       <c r="M16" t="n">
-        <v>0.5151882364934369</v>
+        <v>0.5152642743337853</v>
       </c>
       <c r="N16" t="n">
-        <v>0.9949532175376896</v>
+        <v>0.9951374875422107</v>
       </c>
     </row>
     <row r="17">
@@ -1323,19 +1323,19 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>3.594954591071653</v>
+        <v>3.563006386988963</v>
       </c>
       <c r="E17" t="n">
-        <v>132.6720488156938</v>
+        <v>127.5507170242714</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1400717773887407</v>
+        <v>-0.1483300171368581</v>
       </c>
       <c r="G17" t="n">
-        <v>0.7544699074138658</v>
+        <v>0.7553440976637305</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.1856558837036612</v>
+        <v>-0.1963740996926314</v>
       </c>
       <c r="I17" t="n">
         <v>0.4720416124837452</v>
@@ -1354,10 +1354,10 @@
         </is>
       </c>
       <c r="M17" t="n">
-        <v>0.7208128820819394</v>
+        <v>0.7205421553059035</v>
       </c>
       <c r="N17" t="n">
-        <v>1.098945515903326</v>
+        <v>1.099736959352777</v>
       </c>
     </row>
     <row r="18">
@@ -1377,19 +1377,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>3.040017613122969</v>
+        <v>3.039215664998987</v>
       </c>
       <c r="E18" t="n">
-        <v>77.83183368294932</v>
+        <v>77.36549844514293</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.4777647755251542</v>
+        <v>-0.4780806451269655</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7399530020023869</v>
+        <v>0.7399702493373848</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.6456690819988227</v>
+        <v>-0.6460809006241379</v>
       </c>
       <c r="I18" t="n">
         <v>0.4644343302990898</v>
@@ -1408,10 +1408,10 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.7648387118577219</v>
+        <v>0.764851524962897</v>
       </c>
       <c r="N18" t="n">
-        <v>1.14363041574184</v>
+        <v>1.143604834689471</v>
       </c>
     </row>
     <row r="19">
@@ -1431,19 +1431,19 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>2.921473064074863</v>
+        <v>2.931310745835447</v>
       </c>
       <c r="E19" t="n">
-        <v>80.1932237133428</v>
+        <v>78.94087940333284</v>
       </c>
       <c r="F19" t="n">
-        <v>0.09058403876230803</v>
+        <v>0.09511830151145295</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4774025591513493</v>
+        <v>0.4773789842588035</v>
       </c>
       <c r="H19" t="n">
-        <v>0.1897435131544623</v>
+        <v>0.1992511288680569</v>
       </c>
       <c r="I19" t="n">
         <v>0.2812667740203972</v>
@@ -1462,10 +1462,10 @@
         </is>
       </c>
       <c r="M19" t="n">
-        <v>0.7160658665975727</v>
+        <v>0.7157382570016766</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6907953641853926</v>
+        <v>0.6904021164122335</v>
       </c>
     </row>
     <row r="20">
@@ -1485,19 +1485,19 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>2.568011725512398</v>
+        <v>2.577182146788737</v>
       </c>
       <c r="E20" t="n">
-        <v>124.352301980703</v>
+        <v>124.9074632165466</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.3237347704403523</v>
+        <v>-0.3212486276311108</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7722968116304642</v>
+        <v>0.7721877307728109</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.4191843933123162</v>
+        <v>-0.4160239988656683</v>
       </c>
       <c r="I20" t="n">
         <v>0.443815987933635</v>
@@ -1516,10 +1516,10 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.7321471267324663</v>
+        <v>0.7320799190300141</v>
       </c>
       <c r="N20" t="n">
-        <v>1.142600220772425</v>
+        <v>1.142262653777128</v>
       </c>
     </row>
   </sheetData>
